--- a/data/trans_orig/DC_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/DC_R-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico (incluye Otro dolor crónico) en 2023</t>
+          <t>Población con dolor crónico (incluye Otro dolor crónico) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>135781</t>
+          <t>136739</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>179152</t>
+          <t>178896</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>204943</t>
+          <t>216940</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>302228</t>
+          <t>303478</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>369349</t>
+          <t>386359</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>463139</t>
+          <t>466159</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,26%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>456289</t>
+          <t>456545</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>499660</t>
+          <t>498702</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>423102</t>
+          <t>421852</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>520387</t>
+          <t>508390</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>897633</t>
+          <t>894613</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>991423</t>
+          <t>974413</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>71,61%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>112513</t>
+          <t>92443</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>259818</t>
+          <t>257655</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>361120</t>
+          <t>361002</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>413141</t>
+          <t>410771</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>390670</t>
+          <t>387146</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>671170</t>
+          <t>673678</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,31%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>933046</t>
+          <t>935209</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1080351</t>
+          <t>1100421</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>545510</t>
+          <t>547880</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>597531</t>
+          <t>597649</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1480346</t>
+          <t>1477838</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1760846</t>
+          <t>1764370</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>82,01%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>142779</t>
+          <t>144353</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>192632</t>
+          <t>193976</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>365001</t>
+          <t>364538</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>698819</t>
+          <t>711000</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>516068</t>
+          <t>511311</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>999725</t>
+          <t>973407</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>59,42%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>512048</t>
+          <t>510704</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>561901</t>
+          <t>560327</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>234547</t>
+          <t>222366</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>568365</t>
+          <t>568828</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>638321</t>
+          <t>664639</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1121978</t>
+          <t>1126735</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,79%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>197486</t>
+          <t>199088</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>253420</t>
+          <t>249727</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>419769</t>
+          <t>417398</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>602001</t>
+          <t>588530</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>635878</t>
+          <t>633539</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>882065</t>
+          <t>850434</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>42,06%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>673411</t>
+          <t>677104</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>729345</t>
+          <t>727743</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>492931</t>
+          <t>506402</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>675163</t>
+          <t>677534</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1139698</t>
+          <t>1171329</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1385885</t>
+          <t>1388224</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,66%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>593275</t>
+          <t>570239</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>826212</t>
+          <t>823821</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1469461</t>
+          <t>1468343</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2013722</t>
+          <t>2005111</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2139444</t>
+          <t>2157419</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2875621</t>
+          <t>2827859</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>39,43%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2633605</t>
+          <t>2635996</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2866542</t>
+          <t>2889578</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1698558</t>
+          <t>1707169</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2242819</t>
+          <t>2243937</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4296476</t>
+          <t>4344238</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5032653</t>
+          <t>5014678</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>69,92%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/DC_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/DC_R-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>157098</t>
+          <t>167791</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>136739</t>
+          <t>144424</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>178896</t>
+          <t>189164</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>274039</t>
+          <t>297130</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>216940</t>
+          <t>276357</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>303478</t>
+          <t>320840</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>431137</t>
+          <t>464921</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>386359</t>
+          <t>432553</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>466159</t>
+          <t>497741</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,93%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>478343</t>
+          <t>522919</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>456545</t>
+          <t>501546</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>498702</t>
+          <t>546286</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>451291</t>
+          <t>437050</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>421852</t>
+          <t>413340</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>508390</t>
+          <t>457823</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>929635</t>
+          <t>959968</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>894613</t>
+          <t>927148</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>974413</t>
+          <t>992336</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>69,64%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>197650</t>
+          <t>216435</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>92443</t>
+          <t>190721</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>257655</t>
+          <t>248138</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>386459</t>
+          <t>433846</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>361002</t>
+          <t>403579</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>410771</t>
+          <t>462161</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>584109</t>
+          <t>650281</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>387146</t>
+          <t>609951</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>673678</t>
+          <t>690270</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>32,55%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>995214</t>
+          <t>832482</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>935209</t>
+          <t>800779</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1100421</t>
+          <t>858196</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>572192</t>
+          <t>637628</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>547880</t>
+          <t>609313</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>597649</t>
+          <t>667895</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1567407</t>
+          <t>1470110</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1477838</t>
+          <t>1430121</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1764370</t>
+          <t>1510440</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>71,23%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>167575</t>
+          <t>191823</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>144353</t>
+          <t>167187</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>193976</t>
+          <t>217940</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>500704</t>
+          <t>345442</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>364538</t>
+          <t>320822</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>711000</t>
+          <t>371543</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>668279</t>
+          <t>537264</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>511311</t>
+          <t>502271</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>973407</t>
+          <t>577185</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>35,73%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>537105</t>
+          <t>611250</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>510704</t>
+          <t>585133</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>560327</t>
+          <t>635886</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>432662</t>
+          <t>466817</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>222366</t>
+          <t>440716</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>568828</t>
+          <t>491437</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>969767</t>
+          <t>1078068</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>664639</t>
+          <t>1038147</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1126735</t>
+          <t>1113061</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,91%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>225274</t>
+          <t>233185</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>199088</t>
+          <t>207589</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>249727</t>
+          <t>261470</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>472548</t>
+          <t>438945</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>417398</t>
+          <t>409140</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>588530</t>
+          <t>466899</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>697822</t>
+          <t>672131</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>633539</t>
+          <t>634346</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>850434</t>
+          <t>715443</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>33,92%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>701557</t>
+          <t>756877</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>677104</t>
+          <t>728592</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>727743</t>
+          <t>782473</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>622384</t>
+          <t>680096</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>506402</t>
+          <t>652142</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>677534</t>
+          <t>709901</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1323941</t>
+          <t>1436973</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1171329</t>
+          <t>1393661</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1388224</t>
+          <t>1474758</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>69,92%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>747597</t>
+          <t>809235</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>570239</t>
+          <t>759866</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>823821</t>
+          <t>864592</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1633750</t>
+          <t>1515362</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1468343</t>
+          <t>1464653</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2005111</t>
+          <t>1567010</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2381347</t>
+          <t>2324597</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2157419</t>
+          <t>2244812</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2827859</t>
+          <t>2402482</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>33,05%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2712220</t>
+          <t>2723527</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2635996</t>
+          <t>2668170</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2889578</t>
+          <t>2772896</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2078530</t>
+          <t>2221592</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1707169</t>
+          <t>2169944</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2243937</t>
+          <t>2272301</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4790750</t>
+          <t>4945119</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4344238</t>
+          <t>4867234</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5014678</t>
+          <t>5024904</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,12%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
